--- a/diseases/d120/2000-2004.xlsx
+++ b/diseases/d120/2000-2004.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -7781,9 +7778,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8408,9 +8402,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9083,9 +9074,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9758,9 +9746,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -10433,9 +10418,6 @@
       <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -11108,9 +11090,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11783,9 +11762,6 @@
       <c r="O65" t="n">
         <v>2</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -12458,9 +12434,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -13133,9 +13106,6 @@
       <c r="O73" t="n">
         <v>2</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -13808,9 +13778,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14483,9 +14450,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -15158,9 +15122,6 @@
       <c r="O85" t="n">
         <v>3</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -15833,9 +15794,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -16277,9 +16235,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16673,9 +16628,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16821,9 +16773,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -17513,9 +17462,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -17661,9 +17607,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18353,9 +18296,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18501,9 +18441,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -19193,9 +19130,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19341,9 +19275,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -20033,9 +19964,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20181,9 +20109,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20873,9 +20798,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -21021,9 +20943,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21713,9 +21632,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -21861,9 +21777,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22553,9 +22466,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22701,9 +22611,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -23393,9 +23300,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -23541,9 +23445,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -24233,9 +24134,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24381,9 +24279,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -25073,9 +24968,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -25221,9 +25113,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -25913,9 +25802,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -26061,9 +25947,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -26753,9 +26636,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -27149,9 +27029,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -27297,9 +27174,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -27989,9 +27863,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -28137,9 +28008,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -28829,9 +28697,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -28977,9 +28842,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -29669,9 +29531,6 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -29817,9 +29676,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -30509,9 +30365,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -30657,9 +30510,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -31349,9 +31199,6 @@
       <c r="O181" t="n">
         <v>1</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -31497,9 +31344,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -32189,9 +32033,6 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -32337,9 +32178,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -33029,9 +32867,6 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -33177,9 +33012,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -33869,9 +33701,6 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -34017,9 +33846,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -34709,9 +34535,6 @@
       <c r="O201" t="n">
         <v>1</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -34857,9 +34680,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -35549,9 +35369,6 @@
       <c r="O206" t="n">
         <v>1</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -35697,9 +35514,6 @@
       <c r="O207" t="n">
         <v>1</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -36389,9 +36203,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -36537,9 +36348,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -37229,9 +37037,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -37625,9 +37430,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -38069,9 +37871,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -38513,9 +38312,6 @@
       <c r="O224" t="n">
         <v>1</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -38957,9 +38753,6 @@
       <c r="O227" t="n">
         <v>3</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.006289693798941615</v>
       </c>
@@ -39401,9 +39194,6 @@
       <c r="O230" t="n">
         <v>2</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -39845,9 +39635,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -40289,9 +40076,6 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -40733,9 +40517,6 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -41177,9 +40958,6 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -41621,9 +41399,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -42065,9 +41840,6 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -42508,9 +42280,6 @@
       </c>
       <c r="O251" t="n">
         <v>1</v>
-      </c>
-      <c r="Q251" t="n">
-        <v>0</v>
       </c>
       <c r="R251" t="n">
         <v>0.002096564599647205</v>
